--- a/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C45F60F-A5CC-654A-8228-D00BFAC72E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1A2959-D903-BF4C-BC92-2C84387650B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
+    <workbookView xWindow="700" yWindow="780" windowWidth="27620" windowHeight="15160" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Trek Checkpoint SL (gen 3) 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="132">
   <si>
     <t>model</t>
   </si>
@@ -128,12 +128,6 @@
     <t>material</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -324,6 +318,120 @@
   </si>
   <si>
     <t>a10:h33</t>
+  </si>
+  <si>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>t47</t>
+  </si>
+  <si>
+    <t>46/30</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
@@ -333,7 +441,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -378,6 +486,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -399,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -410,7 +524,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2227,7 +2345,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
+      <xdr:colOff>622300</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2797,32 +2915,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3856DE37-3828-6849-A98A-EC05E320BDEE}">
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AH51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.1640625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="1"/>
+    <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
+    <col min="7" max="9" width="14" style="1" customWidth="1"/>
+    <col min="10" max="13" width="10.83203125" style="1"/>
+    <col min="14" max="14" width="12.1640625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2830,7 +2954,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2838,57 +2962,228 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="B6" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q6" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="R6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="S6" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="V6" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="W6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="X6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y6" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z6" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA6" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB6" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC6" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD6" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE6" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF6" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG6" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH6" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
-      <c r="AC8" s="10"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="D7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="1">
+        <v>44</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>180</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>180</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>2599.9899999999998</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>3199.99</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
@@ -2907,27 +3202,27 @@
       <c r="AB9" s="5"/>
       <c r="AC9" s="5"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="F10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>27</v>
@@ -2946,12 +3241,12 @@
       <c r="AB10" s="6"/>
       <c r="AC10" s="6"/>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" s="6">
         <v>700</v>
@@ -2973,25 +3268,25 @@
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
@@ -3006,12 +3301,12 @@
       <c r="AB11" s="6"/>
       <c r="AC11" s="6"/>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" s="6">
         <f>L12*10</f>
@@ -3039,7 +3334,7 @@
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L12" s="4">
         <v>44.5</v>
@@ -3072,12 +3367,12 @@
       <c r="AB12" s="6"/>
       <c r="AC12" s="6"/>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="6">
         <f>L13</f>
@@ -3105,7 +3400,7 @@
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L13" s="4">
         <v>74</v>
@@ -3138,12 +3433,12 @@
       <c r="AB13" s="6"/>
       <c r="AC13" s="6"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" s="6">
         <f>L14</f>
@@ -3171,7 +3466,7 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L14" s="4">
         <v>72.7</v>
@@ -3204,12 +3499,12 @@
       <c r="AB14" s="6"/>
       <c r="AC14" s="6"/>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="6">
         <f>L15*10</f>
@@ -3237,7 +3532,7 @@
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L15" s="4">
         <v>8.6</v>
@@ -3270,12 +3565,12 @@
       <c r="AB15" s="6"/>
       <c r="AC15" s="6"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" s="6">
         <f>L16</f>
@@ -3303,7 +3598,7 @@
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L16" s="4">
         <v>71</v>
@@ -3337,7 +3632,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="6">
         <f>L17*10</f>
@@ -3365,7 +3660,7 @@
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L17" s="4">
         <v>53.6</v>
@@ -3391,7 +3686,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" s="6">
         <f>L18*10</f>
@@ -3419,7 +3714,7 @@
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L18" s="4">
         <v>7.6</v>
@@ -3445,7 +3740,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="6">
         <f t="shared" ref="C19:C25" si="5">L19*10</f>
@@ -3473,7 +3768,7 @@
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L19" s="4">
         <v>43</v>
@@ -3499,7 +3794,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="6">
         <f t="shared" si="5"/>
@@ -3527,7 +3822,7 @@
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L20" s="4">
         <v>4.9000000000000004</v>
@@ -3553,7 +3848,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="6">
         <f t="shared" si="5"/>
@@ -3580,7 +3875,7 @@
         <v>62</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L21" s="4">
         <v>7.1</v>
@@ -3606,7 +3901,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="6">
         <f t="shared" si="5"/>
@@ -3633,7 +3928,7 @@
         <v>1062</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L22" s="1">
         <v>101.3</v>
@@ -3659,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="6">
         <f t="shared" si="5"/>
@@ -3686,7 +3981,7 @@
         <v>861</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L23" s="1">
         <v>74.599999999999994</v>
@@ -3712,7 +4007,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" s="6">
         <f t="shared" si="5"/>
@@ -3739,7 +4034,7 @@
         <v>408</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L24" s="1">
         <v>38</v>
@@ -3765,7 +4060,7 @@
         <v>8</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" s="6">
         <f t="shared" si="5"/>
@@ -3792,7 +4087,7 @@
         <v>640</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L25" s="1">
         <v>53.5</v>
@@ -4002,7 +4297,7 @@
     </row>
     <row r="36" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C36"/>
       <c r="D36"/>
@@ -4013,141 +4308,141 @@
       <c r="D37"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
+      <c r="B38" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B39" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="8" t="s">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="11"/>
+      <c r="C41" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="10"/>
-      <c r="C41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C42" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="10" t="s">
+      <c r="D42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="11"/>
+      <c r="C43" t="s">
         <v>70</v>
       </c>
-      <c r="C42" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="10"/>
-      <c r="C43" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C44" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="10" t="s">
+      <c r="D44" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="11"/>
+      <c r="C45" t="s">
         <v>75</v>
       </c>
-      <c r="C44" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="11" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="10"/>
-      <c r="C45" t="s">
-        <v>77</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C46" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="10" t="s">
+      <c r="D46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="11"/>
+      <c r="C47" t="s">
         <v>80</v>
       </c>
-      <c r="C46" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="11" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="10"/>
-      <c r="C47" t="s">
-        <v>82</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C48" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="10" t="s">
+      <c r="D48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B49" s="11"/>
+      <c r="C49" t="s">
         <v>85</v>
       </c>
-      <c r="C48" t="s">
-        <v>86</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B50" s="11" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B49" s="10"/>
-      <c r="C49" t="s">
-        <v>87</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C50" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B50" s="10" t="s">
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B51" s="11"/>
+      <c r="C51" t="s">
         <v>90</v>
       </c>
-      <c r="C50" t="s">
-        <v>91</v>
-      </c>
-      <c r="D50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B51" s="10"/>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>92</v>
-      </c>
-      <c r="D51" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811FBA5F-16F9-ED4A-8AF5-553E6A4756B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEF3D30-D044-4946-B8D2-812F36944A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13360" yWindow="2780" windowWidth="20520" windowHeight="15020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8280" yWindow="2780" windowWidth="20520" windowHeight="15020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>us</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -710,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1365,281 +1383,305 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="C34">
-        <f>((622 + 2*C28)/2*COS(C14*PI()/180) - C18)/SIN(C14*PI()/180)</f>
+        <f t="shared" ref="C34:H34" si="0">((622 + 2*C28)/2*COS(C14*PI()/180) - C18)/SIN(C14*PI()/180)</f>
         <v>69.724234113105013</v>
       </c>
       <c r="D34">
-        <f>((622 + 2*D28)/2*COS(D14*PI()/180) - D18)/SIN(D14*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>67.09723125460097</v>
       </c>
       <c r="E34">
-        <f>((622 + 2*E28)/2*COS(E14*PI()/180) - E18)/SIN(E14*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>65.787425623859946</v>
       </c>
       <c r="F34">
-        <f>((622 + 2*F28)/2*COS(F14*PI()/180) - F18)/SIN(F14*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>63.175003782540848</v>
       </c>
       <c r="G34">
-        <f>((622 + 2*G28)/2*COS(G14*PI()/180) - G18)/SIN(G14*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>62.523366931096284</v>
       </c>
       <c r="H34">
-        <f>((622 + 2*H28)/2*COS(H14*PI()/180) - H18)/SIN(H14*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>60.57190170419139</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>117</v>
+      </c>
+      <c r="B36" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>62</v>
+      </c>
+      <c r="B38" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="B46" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>86</v>
+      </c>
+      <c r="B53" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>99</v>
-      </c>
-      <c r="B59" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>104</v>
+        <v>101</v>
+      </c>
+      <c r="B63" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="B64" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B66" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>106</v>
+      </c>
+      <c r="B68" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>108</v>
+      </c>
+      <c r="B69" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>111</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B71" t="s">
         <v>112</v>
       </c>
     </row>

--- a/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEF3D30-D044-4946-B8D2-812F36944A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108D9D91-BD65-B547-8A0C-82D9E407C74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="2780" windowWidth="20520" windowHeight="15020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8280" yWindow="2780" windowWidth="29460" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -68,9 +68,6 @@
     <t>data_range</t>
   </si>
   <si>
-    <t>a8:h31</t>
-  </si>
-  <si>
     <t>frame_size</t>
   </si>
   <si>
@@ -390,6 +387,12 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>a8:h32</t>
   </si>
 </sst>
 </file>
@@ -728,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -778,42 +781,42 @@
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>11</v>
+      <c r="B7" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
       </c>
       <c r="C9">
         <v>700</v>
@@ -836,10 +839,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
       </c>
       <c r="C10">
         <v>445</v>
@@ -862,10 +865,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
       </c>
       <c r="C11">
         <v>74</v>
@@ -888,10 +891,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
       <c r="C12">
         <v>72.7</v>
@@ -914,10 +917,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
       </c>
       <c r="C13">
         <v>86</v>
@@ -940,10 +943,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
         <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
       </c>
       <c r="C14">
         <v>71</v>
@@ -966,10 +969,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
         <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
       </c>
       <c r="C15">
         <v>536</v>
@@ -992,10 +995,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
       </c>
       <c r="C16">
         <v>76</v>
@@ -1018,10 +1021,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
       </c>
       <c r="C17">
         <v>430</v>
@@ -1044,10 +1047,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
       </c>
       <c r="C18">
         <v>49</v>
@@ -1070,10 +1073,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
       </c>
       <c r="C19">
         <v>71</v>
@@ -1096,10 +1099,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
       </c>
       <c r="C20">
         <v>1013</v>
@@ -1122,10 +1125,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
       </c>
       <c r="C21">
         <v>746</v>
@@ -1148,10 +1151,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
         <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
       </c>
       <c r="C22">
         <v>380</v>
@@ -1174,10 +1177,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
         <v>48</v>
-      </c>
-      <c r="B23" t="s">
-        <v>49</v>
       </c>
       <c r="C23">
         <v>535</v>
@@ -1199,490 +1202,495 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24">
-        <v>415</v>
-      </c>
-      <c r="D24">
-        <v>415</v>
-      </c>
-      <c r="E24">
-        <v>415</v>
-      </c>
-      <c r="F24">
-        <v>415</v>
-      </c>
-      <c r="G24">
-        <v>415</v>
-      </c>
-      <c r="H24">
-        <v>415</v>
+      <c r="A24" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="C25">
+        <v>415</v>
+      </c>
+      <c r="D25">
+        <v>415</v>
+      </c>
+      <c r="E25">
+        <v>415</v>
+      </c>
+      <c r="F25">
+        <v>415</v>
+      </c>
+      <c r="G25">
+        <v>415</v>
+      </c>
+      <c r="H25">
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26">
-        <v>70</v>
-      </c>
-      <c r="D26">
-        <v>80</v>
-      </c>
-      <c r="E26">
-        <v>80</v>
-      </c>
-      <c r="F26">
-        <v>90</v>
-      </c>
-      <c r="G26">
-        <v>90</v>
-      </c>
-      <c r="H26">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="C27">
+        <v>70</v>
+      </c>
+      <c r="D27">
+        <v>80</v>
+      </c>
+      <c r="E27">
+        <v>80</v>
+      </c>
+      <c r="F27">
+        <v>90</v>
+      </c>
+      <c r="G27">
+        <v>90</v>
+      </c>
+      <c r="H27">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28">
-        <v>42</v>
-      </c>
-      <c r="D28">
-        <v>42</v>
-      </c>
-      <c r="E28">
-        <v>42</v>
-      </c>
-      <c r="F28">
-        <v>42</v>
-      </c>
-      <c r="G28">
-        <v>42</v>
-      </c>
-      <c r="H28">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C29">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D29">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E29">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F29">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G29">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H29">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C30">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="D30">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="E30">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="F30">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="G30">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="H30">
-        <v>194</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C31">
+        <v>143</v>
+      </c>
+      <c r="D31">
         <v>158</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>164</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>177</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>188</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>194</v>
       </c>
-      <c r="H31">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32">
+        <v>158</v>
+      </c>
+      <c r="D32">
+        <v>164</v>
+      </c>
+      <c r="E32">
+        <v>177</v>
+      </c>
+      <c r="F32">
+        <v>188</v>
+      </c>
+      <c r="G32">
+        <v>194</v>
+      </c>
+      <c r="H32">
         <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
         <v>113</v>
       </c>
-      <c r="B34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34">
-        <f t="shared" ref="C34:H34" si="0">((622 + 2*C28)/2*COS(C14*PI()/180) - C18)/SIN(C14*PI()/180)</f>
+      <c r="C35">
+        <f t="shared" ref="C35:H35" si="0">((622 + 2*C29)/2*COS(C14*PI()/180) - C18)/SIN(C14*PI()/180)</f>
         <v>69.724234113105013</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <f t="shared" si="0"/>
         <v>67.09723125460097</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <f t="shared" si="0"/>
         <v>65.787425623859946</v>
       </c>
-      <c r="F34">
+      <c r="F35">
         <f t="shared" si="0"/>
         <v>63.175003782540848</v>
       </c>
-      <c r="G34">
+      <c r="G35">
         <f t="shared" si="0"/>
         <v>62.523366931096284</v>
       </c>
-      <c r="H34">
+      <c r="H35">
         <f t="shared" si="0"/>
         <v>60.57190170419139</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" t="s">
-        <v>116</v>
-      </c>
-    </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>64</v>
+      </c>
+      <c r="B41" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>68</v>
-      </c>
-      <c r="B42" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>77</v>
+      </c>
+      <c r="B49" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>89</v>
+      </c>
+      <c r="B56" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>92</v>
-      </c>
-      <c r="B57" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>93</v>
+      </c>
+      <c r="B59" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>96</v>
-      </c>
-      <c r="B60" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B62" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="B66" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>106</v>
-      </c>
-      <c r="B68" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B69" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>107</v>
+      </c>
+      <c r="B70" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" t="s">
         <v>111</v>
-      </c>
-      <c r="B71" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108D9D91-BD65-B547-8A0C-82D9E407C74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B892DA-FE14-F14B-9183-B1098A377FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="2780" windowWidth="29460" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2780" windowWidth="28800" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -243,9 +243,6 @@
   </si>
   <si>
     <t>fork_suspension</t>
-  </si>
-  <si>
-    <t>no</t>
   </si>
   <si>
     <t>stem_suspension</t>
@@ -782,7 +779,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1203,7 +1200,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -1391,10 +1388,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" t="s">
         <v>112</v>
-      </c>
-      <c r="B35" t="s">
-        <v>113</v>
       </c>
       <c r="C35">
         <f t="shared" ref="C35:H35" si="0">((622 + 2*C29)/2*COS(C14*PI()/180) - C18)/SIN(C14*PI()/180)</f>
@@ -1423,18 +1420,18 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s">
         <v>114</v>
-      </c>
-      <c r="B36" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" t="s">
         <v>116</v>
-      </c>
-      <c r="B37" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1483,66 +1480,57 @@
       <c r="A44" t="s">
         <v>69</v>
       </c>
-      <c r="B44" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>72</v>
-      </c>
-      <c r="B46" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" t="s">
         <v>73</v>
-      </c>
-      <c r="B47" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" t="s">
         <v>75</v>
-      </c>
-      <c r="B48" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" t="s">
         <v>77</v>
-      </c>
-      <c r="B49" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" t="s">
         <v>80</v>
-      </c>
-      <c r="B51" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
@@ -1550,52 +1538,52 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" t="s">
         <v>83</v>
-      </c>
-      <c r="B53" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" t="s">
         <v>85</v>
-      </c>
-      <c r="B54" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" t="s">
         <v>87</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>90</v>
+      </c>
+      <c r="B58" t="s">
         <v>91</v>
-      </c>
-      <c r="B58" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B59" t="s">
         <v>62</v>
@@ -1603,12 +1591,12 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B61" t="s">
         <v>62</v>
@@ -1616,31 +1604,31 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" t="s">
         <v>96</v>
-      </c>
-      <c r="B62" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>97</v>
+      </c>
+      <c r="B63" t="s">
         <v>98</v>
-      </c>
-      <c r="B63" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
         <v>62</v>
@@ -1648,7 +1636,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
         <v>62</v>
@@ -1656,41 +1644,41 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>104</v>
+      </c>
+      <c r="B69" t="s">
         <v>105</v>
-      </c>
-      <c r="B69" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>106</v>
+      </c>
+      <c r="B70" t="s">
         <v>107</v>
-      </c>
-      <c r="B70" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>109</v>
+      </c>
+      <c r="B72" t="s">
         <v>110</v>
-      </c>
-      <c r="B72" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B892DA-FE14-F14B-9183-B1098A377FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A16F899-3F1E-F945-A1C8-7FBBF5714D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2780" windowWidth="28800" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>a8:h32</t>
+  </si>
+  <si>
+    <t>https://media.trekbikes.com/image/upload/w_1920,h_1440,c_pad,f_auto,fl_progressive:semi,q_auto/CheckpointSL7AXS-26-55097-A-Primary</t>
   </si>
 </sst>
 </file>
@@ -774,6 +777,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A16F899-3F1E-F945-A1C8-7FBBF5714D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC5A456-92A3-F94F-8170-8E781D194632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2780" windowWidth="28800" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13000" yWindow="3240" windowWidth="28800" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -365,9 +365,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -393,6 +390,15 @@
   </si>
   <si>
     <t>https://media.trekbikes.com/image/upload/w_1920,h_1440,c_pad,f_auto,fl_progressive:semi,q_auto/CheckpointSL7AXS-26-55097-A-Primary</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Waterloo, Wisconsin, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -731,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -779,7 +785,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -787,7 +793,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1208,7 +1214,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -1396,10 +1402,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
         <v>111</v>
-      </c>
-      <c r="B35" t="s">
-        <v>112</v>
       </c>
       <c r="C35">
         <f t="shared" ref="C35:H35" si="0">((622 + 2*C29)/2*COS(C14*PI()/180) - C18)/SIN(C14*PI()/180)</f>
@@ -1428,18 +1434,18 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s">
         <v>113</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
         <v>115</v>
-      </c>
-      <c r="B37" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1685,8 +1691,16 @@
       <c r="A72" t="s">
         <v>109</v>
       </c>
-      <c r="B72" t="s">
-        <v>110</v>
+      <c r="B72" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint SL (gen 3) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC5A456-92A3-F94F-8170-8E781D194632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EF3EAE-FF96-9945-BBEA-39455E797B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13000" yWindow="3240" windowWidth="28800" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3240" windowWidth="28800" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -399,6 +399,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -737,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1523,126 +1541,111 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>79</v>
-      </c>
-      <c r="B51" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>81</v>
-      </c>
-      <c r="B52" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>82</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>84</v>
-      </c>
-      <c r="B54" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>88</v>
-      </c>
-      <c r="B56" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>79</v>
+      </c>
+      <c r="B57" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>84</v>
+      </c>
+      <c r="B60" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>97</v>
-      </c>
-      <c r="B63" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B65" t="s">
         <v>62</v>
@@ -1650,56 +1653,101 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>101</v>
-      </c>
-      <c r="B66" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>94</v>
+      </c>
+      <c r="B67" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>95</v>
+      </c>
+      <c r="B68" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+      <c r="B71" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>109</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>121</v>
+        <v>101</v>
+      </c>
+      <c r="B72" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>106</v>
+      </c>
+      <c r="B76" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>109</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>119</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>120</v>
       </c>
     </row>
